--- a/tests/test_adv_analytics.xlsx
+++ b/tests/test_adv_analytics.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="150">
-  <si>
-    <t>उन्नत सेक्टर विश्लेषण डेटाबेस / Sector Detailed Analytics Database — August 2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="165">
+  <si>
+    <t>उन्नत सेक्टर विश्लेषण डेटाबेस / Sector Detailed Analytics Database — October 2026</t>
   </si>
   <si>
     <t>KEY</t>
@@ -26,7 +26,7 @@
     <t>FORMULA_VALUE</t>
   </si>
   <si>
-    <t>जिला कार्यालय बैतूल · म.प्र. राज्य नागरिक आपूर्ति निगम | Report Date: 30/07/2026</t>
+    <t>जिला कार्यालय बैतूल · म.प्र. राज्य नागरिक आपूर्ति निगम | Report Date: 19/09/2026</t>
   </si>
   <si>
     <t>Total Allocation</t>
@@ -343,7 +343,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>📊 कार्यकारी डैशबोर्ड / Executive Analytics Dashboard — August 2026</t>
+    <t>📊 कार्यकारी डैशबोर्ड / Executive Analytics Dashboard — October 2026</t>
   </si>
   <si>
     <t>मध्य प्रदेश राज्य नागरिक आपूर्ति निगम, जिला कार्यालय बैतूल | NFSA मासिक उठाव एवं POS समीक्षा</t>
@@ -373,7 +373,7 @@
     <t>उत्कृष्ट सेक्टर / Excellent Sectors (&gt;=95%)</t>
   </si>
   <si>
-    <t>ब्लॉक-वार उठाव प्रदर्शन सारांश / Block-wise Lifting Performance Summary — August 2026</t>
+    <t>ब्लॉक-वार उठाव प्रदर्शन सारांश / Block-wise Lifting Performance Summary — October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Block Name
@@ -399,22 +399,25 @@
     <t>कुल योग (TOTAL)</t>
   </si>
   <si>
-    <t>परिवहनकर्ता कार्यक्षमता एवं क्षमता समीक्षा / Transporter Performance &amp; Capacity Analysis — August 2026</t>
+    <t>परिवहनकर्ता कार्यक्षमता एवं क्षमता समीक्षा / Transporter Performance &amp; Capacity Analysis — October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Transporter Name
 परिवहनकर्ता नाम</t>
   </si>
   <si>
-    <t xml:space="preserve">Sectors Assigned
-आवंटित सेक्टर</t>
+    <t xml:space="preserve">Sector / Block
+सेक्टर / ब्लॉक</t>
   </si>
   <si>
     <t xml:space="preserve">Capacity Remark
 क्षमता टिप्पणी</t>
   </si>
   <si>
-    <t>🎯 प्राथमिकता कार्रवाई योजना / Priority Action Plan (Lift % &lt; 85%) — August 2026</t>
+    <t>बैतूल सेक्टर क्र 2, भीमपुर सेक्टर क्र 11</t>
+  </si>
+  <si>
+    <t>🎯 प्राथमिकता कार्रवाई योजना / Priority Action Plan (Lift % &lt; 85%) — October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Transporter &amp; Mobile
@@ -428,70 +431,122 @@
     <t>गंभीर</t>
   </si>
   <si>
+    <t>श्री रविन्द्र सिंह तोमर (9893903157)</t>
+  </si>
+  <si>
+    <t>48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours</t>
+  </si>
+  <si>
+    <t>श्री विरेन्द्र परिहार (7389431405)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+17.6%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री नीतेश साहू (9755829852)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+15.9%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री जितेन्द्र सिंह (9399942746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+17.8%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री ओमप्रकाश भोपते (8989100399)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+19.9%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री दुर्गादास सोनारे (9975003109)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+21.3%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री राहुल परिहार (7489479209)</t>
+  </si>
+  <si>
+    <t>श्री सुभाष राठौर (9406566700)</t>
+  </si>
+  <si>
+    <t>श्री पीयूष आर्य (9977060636)</t>
+  </si>
+  <si>
+    <t>श्री साजन राठौर (9685311795)</t>
+  </si>
+  <si>
+    <t>श्री योगेश यादव (7089363619)</t>
+  </si>
+  <si>
+    <t>श्री सौरभ भारद्वाज (8109700701)</t>
+  </si>
+  <si>
+    <t>श्री नीलू रैचे (9806081360)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+26.0%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री निलेश सोनी (9754226851)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+32.5%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री विनोद यादव (9009236960)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+15.2%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
     <t>श्री प्रदीप सिंह (6268969949)</t>
   </si>
   <si>
-    <t>48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours</t>
-  </si>
-  <si>
-    <t>श्री सौरभ भारद्वाज (8109700701)</t>
-  </si>
-  <si>
-    <t>श्री नीतेश साहू (9755829852)</t>
-  </si>
-  <si>
-    <t>श्री राहुल परिहार (7489479209)</t>
-  </si>
-  <si>
-    <t>श्री रविन्द्र सिंह तोमर (9893903157)</t>
-  </si>
-  <si>
-    <t>श्री साजन राठौर (9685311795)</t>
-  </si>
-  <si>
-    <t>श्री योगेश यादव (7089363619)</t>
-  </si>
-  <si>
-    <t>श्री पीयूष आर्य (9977060636)</t>
-  </si>
-  <si>
-    <t>श्री जितेन्द्र सिंह (9399942746)</t>
-  </si>
-  <si>
-    <t>श्री विनोद यादव (9009236960)</t>
-  </si>
-  <si>
     <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
-[ध्वज: POS फीडिंग विलंब (+20.4 pp) - दुकान स्तर एंट्री सत्यापित करें]</t>
-  </si>
-  <si>
-    <t>श्री विरेन्द्र परिहार (7389431405)</t>
+[ध्वज: POS फीडिंग विलंब (+31.5%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री प्रितम कावरे (9644152518)</t>
   </si>
   <si>
     <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
-[ध्वज: POS फीडिंग विलंब (+15.6 pp) - दुकान स्तर एंट्री सत्यापित करें]</t>
-  </si>
-  <si>
-    <t>निगरानी</t>
-  </si>
-  <si>
-    <t>श्री ओमप्रकाश भोपते (8989100399)</t>
-  </si>
-  <si>
-    <t>साप्ताहिक समीक्षा एवं नियमित अनुश्रवण करें / Weekly review &amp; regular monitoring</t>
-  </si>
-  <si>
-    <t>श्री प्रितम कावरे (9644152518)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">साप्ताहिक समीक्षा एवं नियमित अनुश्रवण करें / Weekly review &amp; regular monitoring
-[ध्वज: POS फीडिंग विलंब (+29.3 pp) - दुकान स्तर एंट्री सत्यापित करें]</t>
-  </si>
-  <si>
-    <t>श्री दुर्गादास सोनारे (9975003109)</t>
+[ध्वज: POS फीडिंग विलंब (+37.3%) - दुकान स्तर एंट्री सत्यापित करें]</t>
   </si>
   <si>
     <t>श्री मुकेश राठौर (8319253402)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+24.2%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री दिनेश लिखितकर (9770142072)</t>
+  </si>
+  <si>
+    <t>श्री अंकित राठौर (9425006557)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+29.8%) - दुकान स्तर एंट्री सत्यापित करें]</t>
+  </si>
+  <si>
+    <t>श्री अभिषेक मालवीय (9669921969)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 घंटे के भीतर प्रदाय सुनिश्चित करें एवं समीक्षा करें / Ensure dispatch &amp; review within 48 hours
+[ध्वज: POS फीडिंग विलंब (+23.1%) - दुकान स्तर एंट्री सत्यापित करें]</t>
   </si>
 </sst>
 </file>
@@ -731,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -792,9 +847,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1267,16 +1319,16 @@
         <v>29</v>
       </c>
       <c r="E4" s="6">
-        <v>3493.4</v>
+        <v>3570.5100000000007</v>
       </c>
       <c r="F4" s="6">
-        <v>1626.0299999999997</v>
+        <v>1528.85</v>
       </c>
       <c r="G4" s="4">
         <f>F4/E4</f>
       </c>
       <c r="H4" s="4">
-        <f>1126.9300000000003/E4</f>
+        <f>402.8/E4</f>
       </c>
       <c r="I4" s="4">
         <f>(F4/E4 - H4)*100</f>
@@ -1317,16 +1369,16 @@
         <v>36</v>
       </c>
       <c r="E5" s="9">
-        <v>3624.5500000000006</v>
+        <v>3830.8399999999992</v>
       </c>
       <c r="F5" s="9">
-        <v>2414.56</v>
+        <v>1552.5699999999997</v>
       </c>
       <c r="G5" s="7">
         <f>F5/E5</f>
       </c>
       <c r="H5" s="7">
-        <f>2290.0499999999997/E5</f>
+        <f>556.8900000000001/E5</f>
       </c>
       <c r="I5" s="7">
         <f>(F5/E5 - H5)*100</f>
@@ -1367,16 +1419,16 @@
         <v>38</v>
       </c>
       <c r="E6" s="6">
-        <v>3795.8600000000015</v>
+        <v>4000.3199999999993</v>
       </c>
       <c r="F6" s="6">
-        <v>2306.07</v>
+        <v>1126.12</v>
       </c>
       <c r="G6" s="4">
         <f>F6/E6</f>
       </c>
       <c r="H6" s="4">
-        <f>2123.74/E6</f>
+        <f>603.7500000000001/E6</f>
       </c>
       <c r="I6" s="4">
         <f>(F6/E6 - H6)*100</f>
@@ -1417,16 +1469,16 @@
         <v>24</v>
       </c>
       <c r="E7" s="9">
-        <v>2859.9500000000003</v>
+        <v>3060.3300000000004</v>
       </c>
       <c r="F7" s="9">
-        <v>1924.2900000000002</v>
+        <v>1299.97</v>
       </c>
       <c r="G7" s="7">
         <f>F7/E7</f>
       </c>
       <c r="H7" s="7">
-        <f>1342.03/E7</f>
+        <f>833.68/E7</f>
       </c>
       <c r="I7" s="7">
         <f>(F7/E7 - H7)*100</f>
@@ -1467,16 +1519,16 @@
         <v>33</v>
       </c>
       <c r="E8" s="6">
-        <v>2865.6499999999987</v>
+        <v>3051.270000000001</v>
       </c>
       <c r="F8" s="6">
-        <v>2054.3099999999995</v>
+        <v>1417.7699999999995</v>
       </c>
       <c r="G8" s="4">
         <f>F8/E8</f>
       </c>
       <c r="H8" s="4">
-        <f>1214.42/E8</f>
+        <f>280.95000000000005/E8</f>
       </c>
       <c r="I8" s="4">
         <f>(F8/E8 - H8)*100</f>
@@ -1517,16 +1569,16 @@
         <v>17</v>
       </c>
       <c r="E9" s="9">
-        <v>2336.2200000000003</v>
+        <v>2516.99</v>
       </c>
       <c r="F9" s="9">
-        <v>1514.5499999999997</v>
+        <v>840.44</v>
       </c>
       <c r="G9" s="7">
         <f>F9/E9</f>
       </c>
       <c r="H9" s="7">
-        <f>1390.5799999999997/E9</f>
+        <f>549.1800000000001/E9</f>
       </c>
       <c r="I9" s="7">
         <f>(F9/E9 - H9)*100</f>
@@ -1567,16 +1619,16 @@
         <v>25</v>
       </c>
       <c r="E10" s="6">
-        <v>2685.1</v>
+        <v>2846.82</v>
       </c>
       <c r="F10" s="6">
-        <v>2259.9199999999996</v>
+        <v>1634.7600000000004</v>
       </c>
       <c r="G10" s="4">
         <f>F10/E10</f>
       </c>
       <c r="H10" s="4">
-        <f>1955.3600000000001/E10</f>
+        <f>944.89/E10</f>
       </c>
       <c r="I10" s="4">
         <f>(F10/E10 - H10)*100</f>
@@ -1611,16 +1663,16 @@
         <v>26</v>
       </c>
       <c r="E11" s="9">
-        <v>3017.55</v>
+        <v>3200.6599999999994</v>
       </c>
       <c r="F11" s="9">
-        <v>2795.4</v>
+        <v>2103.8499999999995</v>
       </c>
       <c r="G11" s="7">
         <f>F11/E11</f>
       </c>
       <c r="H11" s="7">
-        <f>2139.3199999999997/E11</f>
+        <f>1149.6300000000003/E11</f>
       </c>
       <c r="I11" s="7">
         <f>(F11/E11 - H11)*100</f>
@@ -1655,16 +1707,16 @@
         <v>29</v>
       </c>
       <c r="E12" s="6">
-        <v>2793.84</v>
+        <v>2936.4000000000015</v>
       </c>
       <c r="F12" s="6">
-        <v>1512.25</v>
+        <v>1072.2899999999997</v>
       </c>
       <c r="G12" s="4">
         <f>F12/E12</f>
       </c>
       <c r="H12" s="4">
-        <f>1485.8399999999997/E12</f>
+        <f>866.5699999999999/E12</f>
       </c>
       <c r="I12" s="4">
         <f>(F12/E12 - H12)*100</f>
@@ -1699,16 +1751,16 @@
         <v>25</v>
       </c>
       <c r="E13" s="9">
-        <v>2823.7900000000013</v>
+        <v>2954.569999999999</v>
       </c>
       <c r="F13" s="9">
-        <v>2651.7300000000014</v>
+        <v>1118.09</v>
       </c>
       <c r="G13" s="7">
         <f>F13/E13</f>
       </c>
       <c r="H13" s="7">
-        <f>2520.2500000000014/E13</f>
+        <f>877.3599999999999/E13</f>
       </c>
       <c r="I13" s="7">
         <f>(F13/E13 - H13)*100</f>
@@ -1743,16 +1795,16 @@
         <v>22</v>
       </c>
       <c r="E14" s="6">
-        <v>2916.9200000000014</v>
+        <v>3059.3699999999994</v>
       </c>
       <c r="F14" s="6">
-        <v>2041.1299999999999</v>
+        <v>954.6100000000001</v>
       </c>
       <c r="G14" s="4">
         <f>F14/E14</f>
       </c>
       <c r="H14" s="4">
-        <f>1907.79/E14</f>
+        <f>954.6100000000001/E14</f>
       </c>
       <c r="I14" s="4">
         <f>(F14/E14 - H14)*100</f>
@@ -1787,16 +1839,16 @@
         <v>29</v>
       </c>
       <c r="E15" s="9">
-        <v>3123.0299999999997</v>
+        <v>3254.4</v>
       </c>
       <c r="F15" s="9">
-        <v>3112.22</v>
+        <v>2169.88</v>
       </c>
       <c r="G15" s="7">
         <f>F15/E15</f>
       </c>
       <c r="H15" s="7">
-        <f>3112.22/E15</f>
+        <f>1419.2599999999995/E15</f>
       </c>
       <c r="I15" s="7">
         <f>(F15/E15 - H15)*100</f>
@@ -1831,16 +1883,16 @@
         <v>26</v>
       </c>
       <c r="E16" s="6">
-        <v>2717.1400000000003</v>
+        <v>3002.4999999999995</v>
       </c>
       <c r="F16" s="6">
-        <v>2670.2200000000003</v>
+        <v>1946.7400000000002</v>
       </c>
       <c r="G16" s="4">
         <f>F16/E16</f>
       </c>
       <c r="H16" s="4">
-        <f>2670.2200000000003/E16</f>
+        <f>1798.65/E16</f>
       </c>
       <c r="I16" s="4">
         <f>(F16/E16 - H16)*100</f>
@@ -1875,16 +1927,16 @@
         <v>30</v>
       </c>
       <c r="E17" s="9">
-        <v>2853.1500000000005</v>
+        <v>2964.3800000000015</v>
       </c>
       <c r="F17" s="9">
-        <v>2753.25</v>
+        <v>918.9399999999999</v>
       </c>
       <c r="G17" s="7">
         <f>F17/E17</f>
       </c>
       <c r="H17" s="7">
-        <f>2395.6499999999996/E17</f>
+        <f>571.46/E17</f>
       </c>
       <c r="I17" s="7">
         <f>(F17/E17 - H17)*100</f>
@@ -1919,16 +1971,16 @@
         <v>25</v>
       </c>
       <c r="E18" s="6">
-        <v>2705.1499999999996</v>
+        <v>2781.3099999999995</v>
       </c>
       <c r="F18" s="6">
-        <v>2705.1499999999996</v>
+        <v>1130.21</v>
       </c>
       <c r="G18" s="4">
         <f>F18/E18</f>
       </c>
       <c r="H18" s="4">
-        <f>2701.2899999999995/E18</f>
+        <f>227.79/E18</f>
       </c>
       <c r="I18" s="4">
         <f>(F18/E18 - H18)*100</f>
@@ -1963,16 +2015,16 @@
         <v>39</v>
       </c>
       <c r="E19" s="9">
-        <v>2990.7799999999993</v>
+        <v>3359.000000000001</v>
       </c>
       <c r="F19" s="9">
-        <v>2445.6599999999994</v>
+        <v>885.3</v>
       </c>
       <c r="G19" s="7">
         <f>F19/E19</f>
       </c>
       <c r="H19" s="7">
-        <f>2123.49/E19</f>
+        <f>168.51999999999998/E19</f>
       </c>
       <c r="I19" s="7">
         <f>(F19/E19 - H19)*100</f>
@@ -2007,16 +2059,16 @@
         <v>31</v>
       </c>
       <c r="E20" s="6">
-        <v>2852.78</v>
+        <v>3119.759999999998</v>
       </c>
       <c r="F20" s="6">
-        <v>2032.52</v>
+        <v>817.84</v>
       </c>
       <c r="G20" s="4">
         <f>F20/E20</f>
       </c>
       <c r="H20" s="4">
-        <f>1819.2200000000003/E20</f>
+        <f>196.45/E20</f>
       </c>
       <c r="I20" s="4">
         <f>(F20/E20 - H20)*100</f>
@@ -2051,16 +2103,16 @@
         <v>37</v>
       </c>
       <c r="E21" s="9">
-        <v>3377.7099999999996</v>
+        <v>3693.010000000001</v>
       </c>
       <c r="F21" s="9">
-        <v>2270.0899999999992</v>
+        <v>962.7</v>
       </c>
       <c r="G21" s="7">
         <f>F21/E21</f>
       </c>
       <c r="H21" s="7">
-        <f>1813.7999999999993/E21</f>
+        <f>304.8/E21</f>
       </c>
       <c r="I21" s="7">
         <f>(F21/E21 - H21)*100</f>
@@ -2095,16 +2147,16 @@
         <v>39</v>
       </c>
       <c r="E22" s="6">
-        <v>3338.9100000000003</v>
+        <v>3656.2699999999995</v>
       </c>
       <c r="F22" s="6">
-        <v>2320.27</v>
+        <v>735.71</v>
       </c>
       <c r="G22" s="4">
         <f>F22/E22</f>
       </c>
       <c r="H22" s="4">
-        <f>1798.7500000000002/E22</f>
+        <f>90.4/E22</f>
       </c>
       <c r="I22" s="4">
         <f>(F22/E22 - H22)*100</f>
@@ -2139,16 +2191,16 @@
         <v>37</v>
       </c>
       <c r="E23" s="9">
-        <v>3727.1800000000003</v>
+        <v>4274.469999999998</v>
       </c>
       <c r="F23" s="9">
-        <v>2288.7499999999995</v>
+        <v>696.9700000000001</v>
       </c>
       <c r="G23" s="7">
         <f>F23/E23</f>
       </c>
       <c r="H23" s="7">
-        <f>2197.8299999999995/E23</f>
+        <f>115.57/E23</f>
       </c>
       <c r="I23" s="7">
         <f>(F23/E23 - H23)*100</f>
@@ -2183,16 +2235,16 @@
         <v>38</v>
       </c>
       <c r="E24" s="6">
-        <v>3724.369999999999</v>
+        <v>3969.740000000001</v>
       </c>
       <c r="F24" s="6">
-        <v>2108.7999999999993</v>
+        <v>968.54</v>
       </c>
       <c r="G24" s="4">
         <f>F24/E24</f>
       </c>
       <c r="H24" s="4">
-        <f>1592.6899999999998/E24</f>
+        <f>335.59000000000003/E24</f>
       </c>
       <c r="I24" s="4">
         <f>(F24/E24 - H24)*100</f>
@@ -2227,16 +2279,16 @@
         <v>27</v>
       </c>
       <c r="E25" s="9">
-        <v>2755.91</v>
+        <v>2883.4300000000003</v>
       </c>
       <c r="F25" s="9">
-        <v>1812.1799999999996</v>
+        <v>979.4300000000002</v>
       </c>
       <c r="G25" s="7">
         <f>F25/E25</f>
       </c>
       <c r="H25" s="7">
-        <f>1724.86/E25</f>
+        <f>979.4300000000002/E25</f>
       </c>
       <c r="I25" s="7">
         <f>(F25/E25 - H25)*100</f>
@@ -2543,7 +2595,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C5" s="7">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B5)</f>
@@ -2569,7 +2621,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B6)</f>
@@ -2595,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B7)</f>
@@ -2621,7 +2673,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B8)</f>
@@ -2647,7 +2699,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C9" s="7">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B9)</f>
@@ -2673,7 +2725,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B10)</f>
@@ -2699,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C11" s="7">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B11)</f>
@@ -2725,7 +2777,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C12" s="4">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B12)</f>
@@ -2751,7 +2803,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C13" s="7">
         <f>COUNTIF('Sector Detail'!$B$4:$B$25, B13)</f>
@@ -2862,10 +2914,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B4)</f>
+        <v>64</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="D4" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B4, 'Sector Detail'!$E$4:$E$25)</f>
@@ -2880,7 +2932,7 @@
         <f>D4-E4</f>
       </c>
       <c r="H4" s="5">
-        <f>IF(C4&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C4)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2888,10 +2940,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B5)</f>
+        <v>51</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D5" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B5, 'Sector Detail'!$E$4:$E$25)</f>
@@ -2906,7 +2958,7 @@
         <f>D5-E5</f>
       </c>
       <c r="H5" s="8">
-        <f>IF(C5&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C5)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2916,8 +2968,8 @@
       <c r="B6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B6)</f>
+      <c r="C6" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="D6" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B6, 'Sector Detail'!$E$4:$E$25)</f>
@@ -2932,7 +2984,7 @@
         <f>D6-E6</f>
       </c>
       <c r="H6" s="5">
-        <f>IF(C6&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C6)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2940,10 +2992,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B7)</f>
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="D7" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B7, 'Sector Detail'!$E$4:$E$25)</f>
@@ -2958,7 +3010,7 @@
         <f>D7-E7</f>
       </c>
       <c r="H7" s="8">
-        <f>IF(C7&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C7)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2966,10 +3018,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B8)</f>
+        <v>39</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D8" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B8, 'Sector Detail'!$E$4:$E$25)</f>
@@ -2984,7 +3036,7 @@
         <f>D8-E8</f>
       </c>
       <c r="H8" s="5">
-        <f>IF(C8&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C8)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2992,10 +3044,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B9)</f>
+        <v>22</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="D9" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B9, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3010,7 +3062,7 @@
         <f>D9-E9</f>
       </c>
       <c r="H9" s="8">
-        <f>IF(C9&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C9)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3018,10 +3070,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B10)</f>
+        <v>35</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="D10" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B10, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3036,7 +3088,7 @@
         <f>D10-E10</f>
       </c>
       <c r="H10" s="5">
-        <f>IF(C10&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C10)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3044,10 +3096,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B11)</f>
+        <v>74</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="D11" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B11, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3062,7 +3114,7 @@
         <f>D11-E11</f>
       </c>
       <c r="H11" s="8">
-        <f>IF(C11&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C11)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3070,10 +3122,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B12)</f>
+        <v>59</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="D12" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B12, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3088,7 +3140,7 @@
         <f>D12-E12</f>
       </c>
       <c r="H12" s="5">
-        <f>IF(C12&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C12)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3096,10 +3148,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B13)</f>
+        <v>55</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D13" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B13, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3114,7 +3166,7 @@
         <f>D13-E13</f>
       </c>
       <c r="H13" s="8">
-        <f>IF(C13&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C13)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3122,10 +3174,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B14)</f>
+        <v>26</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="D14" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B14, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3139,8 +3191,8 @@
       <c r="G14" s="6">
         <f>D14-E14</f>
       </c>
-      <c r="H14" s="5">
-        <f>IF(C14&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+      <c r="H14" s="20">
+        <f>IF(ISNUMBER(SEARCH(",", C14)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3148,10 +3200,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B15)</f>
+        <v>98</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D15" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B15, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3165,8 +3217,8 @@
       <c r="G15" s="9">
         <f>D15-E15</f>
       </c>
-      <c r="H15" s="20">
-        <f>IF(C15&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+      <c r="H15" s="8">
+        <f>IF(ISNUMBER(SEARCH(",", C15)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3174,10 +3226,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B16)</f>
+        <v>44</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D16" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B16, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3192,7 +3244,7 @@
         <f>D16-E16</f>
       </c>
       <c r="H16" s="5">
-        <f>IF(C16&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C16)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3200,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B17)</f>
+        <v>71</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="D17" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B17, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3218,7 +3270,7 @@
         <f>D17-E17</f>
       </c>
       <c r="H17" s="8">
-        <f>IF(C17&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C17)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3226,10 +3278,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B18)</f>
+        <v>30</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="D18" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B18, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3244,7 +3296,7 @@
         <f>D18-E18</f>
       </c>
       <c r="H18" s="5">
-        <f>IF(C18&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C18)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3252,10 +3304,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B19)</f>
+        <v>78</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="D19" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B19, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3270,7 +3322,7 @@
         <f>D19-E19</f>
       </c>
       <c r="H19" s="8">
-        <f>IF(C19&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C19)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3278,10 +3330,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B20)</f>
+        <v>81</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="D20" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B20, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3296,7 +3348,7 @@
         <f>D20-E20</f>
       </c>
       <c r="H20" s="5">
-        <f>IF(C20&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C20)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3304,10 +3356,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B21)</f>
+        <v>85</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="D21" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B21, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3322,7 +3374,7 @@
         <f>D21-E21</f>
       </c>
       <c r="H21" s="8">
-        <f>IF(C21&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C21)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3332,8 +3384,8 @@
       <c r="B22" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B22)</f>
+      <c r="C22" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="D22" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B22, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3348,7 +3400,7 @@
         <f>D22-E22</f>
       </c>
       <c r="H22" s="5">
-        <f>IF(C22&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C22)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3356,10 +3408,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="7">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B23)</f>
+        <v>88</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="D23" s="9">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B23, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3374,7 +3426,7 @@
         <f>D23-E23</f>
       </c>
       <c r="H23" s="8">
-        <f>IF(C23&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C23)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3382,10 +3434,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="4">
-        <f>COUNTIF('Sector Detail'!$M$4:$M$25, B24)</f>
+        <v>92</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="D24" s="6">
         <f>SUMIF('Sector Detail'!$M$4:$M$25, B24, 'Sector Detail'!$E$4:$E$25)</f>
@@ -3400,7 +3452,7 @@
         <f>D24-E24</f>
       </c>
       <c r="H24" s="5">
-        <f>IF(C24&gt;1, "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
+        <f>IF(ISNUMBER(SEARCH(",", C24)), "एकाधिक सेक्टर — क्षमता जांचें / Multiple sectors — verify capacity", "सामान्य / Normal")</f>
       </c>
     </row>
   </sheetData>
@@ -3414,7 +3466,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3429,7 +3481,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -3459,10 +3511,10 @@
         <v>15</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3470,25 +3522,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4654577202725138</v>
+        <v>0.16305413302701866</v>
       </c>
       <c r="E4" s="6">
-        <v>1867.3700000000003</v>
+        <v>3577.499999999998</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3496,25 +3548,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D5" s="7">
-        <v>0.5412801019385505</v>
+        <v>0.2012187283761867</v>
       </c>
       <c r="E5" s="9">
-        <v>1281.5900000000001</v>
+        <v>2920.5599999999995</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3528,19 +3580,19 @@
         <v>90</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5662165681712611</v>
+        <v>0.24398071410218294</v>
       </c>
       <c r="E6" s="6">
-        <v>1615.5699999999997</v>
+        <v>3001.200000000001</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3548,25 +3600,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D7" s="7">
-        <v>0.6075224059896833</v>
+        <v>0.26068166617474625</v>
       </c>
       <c r="E7" s="9">
-        <v>1489.7900000000013</v>
+        <v>2730.3100000000013</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3574,25 +3626,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D8" s="4">
-        <v>0.614070154916049</v>
+        <v>0.2621483703874659</v>
       </c>
       <c r="E8" s="6">
-        <v>1438.4300000000007</v>
+        <v>2301.919999999998</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3600,25 +3652,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D9" s="7">
-        <v>0.6482908287746871</v>
+        <v>0.26356058350699607</v>
       </c>
       <c r="E9" s="9">
-        <v>821.6700000000005</v>
+        <v>2473.7000000000007</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3626,25 +3678,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4">
-        <v>0.6575613862571709</v>
+        <v>0.2815074794016479</v>
       </c>
       <c r="E10" s="6">
-        <v>943.7300000000002</v>
+        <v>2874.1999999999994</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3652,25 +3704,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D11" s="7">
-        <v>0.6661682139851842</v>
+        <v>0.3099939953717133</v>
       </c>
       <c r="E11" s="9">
-        <v>1209.9900000000007</v>
+        <v>2045.4400000000014</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3678,25 +3730,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4">
-        <v>0.6720796042289005</v>
+        <v>0.3120282934068126</v>
       </c>
       <c r="E12" s="6">
-        <v>1107.6200000000003</v>
+        <v>2104.7599999999993</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3704,25 +3756,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D13" s="7">
-        <v>0.6728404342733264</v>
+        <v>0.3339067695938403</v>
       </c>
       <c r="E13" s="9">
-        <v>935.6600000000001</v>
+        <v>1676.5499999999997</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3730,25 +3782,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D14" s="4">
-        <v>0.6949184015142665</v>
+        <v>0.33967531724369937</v>
       </c>
       <c r="E14" s="6">
-        <v>1018.6400000000003</v>
+        <v>1904</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3756,25 +3808,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D15" s="7">
-        <v>0.6997552212607815</v>
+        <v>0.36517163874131564</v>
       </c>
       <c r="E15" s="9">
-        <v>875.7900000000016</v>
+        <v>1864.1100000000017</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3782,25 +3834,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D16" s="4">
-        <v>0.7124699416008244</v>
+        <v>0.37842731768074556</v>
       </c>
       <c r="E16" s="6">
-        <v>820.2600000000002</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>143</v>
+        <v>1836.4799999999989</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3808,25 +3860,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D17" s="7">
-        <v>0.7168740076422454</v>
+        <v>0.40528187029476564</v>
       </c>
       <c r="E17" s="9">
-        <v>811.3399999999992</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>143</v>
+        <v>2278.2699999999995</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3834,25 +3886,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D18" s="4">
-        <v>0.8177331665986799</v>
+        <v>0.4063588740557508</v>
       </c>
       <c r="E18" s="6">
-        <v>545.1199999999999</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>143</v>
+        <v>1651.0999999999995</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3860,25 +3912,181 @@
         <v>16</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.42478098767126415</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1760.3600000000004</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.42818812998703254</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2041.6600000000008</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.4646491460932658</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1633.5000000000014</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="7">
-        <v>0.8416520799970205</v>
-      </c>
-      <c r="E19" s="9">
-        <v>425.1800000000003</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>145</v>
+      <c r="D22" s="4">
+        <v>0.5742407317638629</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1212.0599999999997</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.6483730224812658</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1055.7599999999993</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.6573175532546411</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1096.81</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0.6667527040314651</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1084.52</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
